--- a/output/yearly_surface_area_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_52_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497606713161</v>
+        <v>10.84497608357739</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890710182323</v>
+        <v>37.78907107553724</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.539020547360504</v>
+        <v>5.404521111878692</v>
       </c>
       <c r="C2" t="n">
-        <v>13.53731909385927</v>
+        <v>8.262388678941157</v>
       </c>
       <c r="D2" t="n">
-        <v>36.65649578116741</v>
+        <v>39.78238047148925</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.07888397370501</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C3" t="n">
-        <v>35.92705723691203</v>
+        <v>26.64954143177967</v>
       </c>
       <c r="D3" t="n">
-        <v>67.73077411598744</v>
+        <v>103.89835954044</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4420738710141</v>
+        <v>36.27165068110266</v>
       </c>
       <c r="C4" t="n">
-        <v>91.73843247563894</v>
+        <v>74.64915018781471</v>
       </c>
       <c r="D4" t="n">
-        <v>99.81723433388595</v>
+        <v>121.8584520419311</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.57072387799944</v>
+        <v>43.07418052382881</v>
       </c>
       <c r="C5" t="n">
-        <v>124.0683661241907</v>
+        <v>111.3792770468007</v>
       </c>
       <c r="D5" t="n">
-        <v>78.29437941368315</v>
+        <v>80.84692344472485</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.70321876034376</v>
+        <v>41.0164373357275</v>
       </c>
       <c r="C6" t="n">
-        <v>139.9952591301867</v>
+        <v>101.1524112116616</v>
       </c>
       <c r="D6" t="n">
-        <v>52.36740429222912</v>
+        <v>48.18123208132072</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.97271635292611</v>
+        <v>29.40432548989622</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2590461629928</v>
+        <v>85.33841919165398</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="C8" t="n">
-        <v>85.45132017764237</v>
+        <v>54.65880343394117</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>48.25780840225195</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.656433442681901</v>
+        <v>7.68655316963059</v>
       </c>
       <c r="C21" t="n">
-        <v>92.83425549251804</v>
+        <v>94.16027632797471</v>
       </c>
       <c r="D21" t="n">
-        <v>7.656433442681901</v>
+        <v>8.647372315834414</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.237043165079987</v>
+        <v>5.712789891012189</v>
       </c>
       <c r="C2" t="n">
-        <v>9.53866069446201</v>
+        <v>9.814531799355363</v>
       </c>
       <c r="D2" t="n">
-        <v>32.88952983997239</v>
+        <v>44.07261793904782</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.10342766631118</v>
+        <v>18.80537727484765</v>
       </c>
       <c r="C3" t="n">
-        <v>43.9233922880023</v>
+        <v>29.24135537099124</v>
       </c>
       <c r="D3" t="n">
-        <v>78.0734861802276</v>
+        <v>109.8379331511331</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.74012426247764</v>
+        <v>36.50137964389641</v>
       </c>
       <c r="C4" t="n">
-        <v>90.58978766167017</v>
+        <v>69.85036740945631</v>
       </c>
       <c r="D4" t="n">
-        <v>107.5386800277871</v>
+        <v>142.3426178910408</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.67581194008286</v>
+        <v>48.42470551197393</v>
       </c>
       <c r="C5" t="n">
-        <v>143.4087958978529</v>
+        <v>123.8720165833413</v>
       </c>
       <c r="D5" t="n">
-        <v>93.36420667387168</v>
+        <v>101.1691009226338</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.83405324691584</v>
+        <v>48.66425195181016</v>
       </c>
       <c r="C6" t="n">
-        <v>166.078332136616</v>
+        <v>135.1650604252924</v>
       </c>
       <c r="D6" t="n">
-        <v>62.10830501376597</v>
+        <v>60.49823877880121</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.63820242768521</v>
+        <v>38.20765715387736</v>
       </c>
       <c r="C7" t="n">
-        <v>160.0769084205552</v>
+        <v>114.0241053620415</v>
       </c>
       <c r="D7" t="n">
-        <v>45.45393695892307</v>
+        <v>43.11835917051991</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.02627050830318</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="C8" t="n">
-        <v>123.1700669748048</v>
+        <v>81.11199532487147</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>11.42656152972862</v>
       </c>
       <c r="C9" t="n">
-        <v>73.32968127330699</v>
+        <v>50.03280825153018</v>
       </c>
       <c r="D9" t="n">
         <v>35.38905949498476</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>42.70602513473626</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.826714094119678</v>
+        <v>7.864209621818022</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7689439617909</v>
+        <v>102.2347250836343</v>
       </c>
       <c r="D21" t="n">
-        <v>8.805053355884638</v>
+        <v>9.830262027272527</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.714573459971436</v>
+        <v>7.003788122096745</v>
       </c>
       <c r="C2" t="n">
-        <v>11.75544701065131</v>
+        <v>8.686503687175778</v>
       </c>
       <c r="D2" t="n">
-        <v>31.25884690321844</v>
+        <v>43.76631265532281</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.84955592153876</v>
+        <v>18.54521413322225</v>
       </c>
       <c r="C3" t="n">
-        <v>40.43818793792612</v>
+        <v>33.10453258720245</v>
       </c>
       <c r="D3" t="n">
-        <v>83.43873738393643</v>
+        <v>116.0671223345792</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.66805576944012</v>
+        <v>35.31444666946201</v>
       </c>
       <c r="C4" t="n">
-        <v>97.57099558656925</v>
+        <v>71.06282582420111</v>
       </c>
       <c r="D4" t="n">
-        <v>118.0041105550581</v>
+        <v>157.2622377524796</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.76202581160733</v>
+        <v>50.60909415392309</v>
       </c>
       <c r="C5" t="n">
-        <v>152.8335738586222</v>
+        <v>124.4119778206771</v>
       </c>
       <c r="D5" t="n">
-        <v>104.8751985061655</v>
+        <v>122.9393562643069</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.03909964838319</v>
+        <v>55.34602682691394</v>
       </c>
       <c r="C6" t="n">
-        <v>189.5852991671016</v>
+        <v>160.0405837554981</v>
       </c>
       <c r="D6" t="n">
-        <v>73.49952362614172</v>
+        <v>73.258013690897</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.06414206260808</v>
+        <v>46.35223610830891</v>
       </c>
       <c r="C7" t="n">
-        <v>191.6970384789364</v>
+        <v>148.9379989681709</v>
       </c>
       <c r="D7" t="n">
-        <v>50.48441219548373</v>
+        <v>49.10702016642545</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.2849121228766</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C8" t="n">
-        <v>159.0529455650257</v>
+        <v>109.9851953067702</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.09062388842696</v>
+        <v>16.08593613408398</v>
       </c>
       <c r="C9" t="n">
-        <v>106.0562409943744</v>
+        <v>70.9999939711293</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>59.78843518863076</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>35.53926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.980210404270085</v>
+        <v>8.025262478309028</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7328404576461</v>
+        <v>110.3473590767491</v>
       </c>
       <c r="D21" t="n">
-        <v>9.975263005337606</v>
+        <v>11.03473590767491</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.077419199915256</v>
+        <v>6.433392705929348</v>
       </c>
       <c r="C2" t="n">
-        <v>8.275151399096364</v>
+        <v>5.975898275750335</v>
       </c>
       <c r="D2" t="n">
-        <v>25.8072019015359</v>
+        <v>36.12635202087413</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.59492341324034</v>
+        <v>23.26251185212817</v>
       </c>
       <c r="C3" t="n">
-        <v>60.67200812245289</v>
+        <v>47.92401418280805</v>
       </c>
       <c r="D3" t="n">
-        <v>90.03608195647499</v>
+        <v>124.431612774762</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.94737083906494</v>
+        <v>24.31298189567226</v>
       </c>
       <c r="C4" t="n">
-        <v>127.8058796342583</v>
+        <v>100.9914045881651</v>
       </c>
       <c r="D4" t="n">
-        <v>115.2473630015331</v>
+        <v>146.8478581058294</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.74066404182538</v>
+        <v>31.17048960983623</v>
       </c>
       <c r="C5" t="n">
-        <v>113.2691413774758</v>
+        <v>95.62222639363934</v>
       </c>
       <c r="D5" t="n">
-        <v>71.10307748007526</v>
+        <v>76.82175785731292</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.87552333020568</v>
+        <v>28.77993394999525</v>
       </c>
       <c r="C6" t="n">
-        <v>126.2291928212379</v>
+        <v>98.09328536522857</v>
       </c>
       <c r="D6" t="n">
-        <v>33.24786775202249</v>
+        <v>32.32207966691774</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>111.8083007935565</v>
+        <v>77.31361345714056</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>78.10784734987622</v>
+        <v>52.32224389783376</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.276492999699106</v>
+        <v>3.927972564691488</v>
       </c>
       <c r="C2" t="n">
-        <v>4.368777283898306</v>
+        <v>2.569233742013903</v>
       </c>
       <c r="D2" t="n">
-        <v>19.11855479250238</v>
+        <v>24.63401339496097</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.93500902953724</v>
+        <v>23.37050409959532</v>
       </c>
       <c r="C3" t="n">
-        <v>47.66875977970388</v>
+        <v>36.11358930071892</v>
       </c>
       <c r="D3" t="n">
-        <v>89.9820858327414</v>
+        <v>126.1005838719816</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.56220694383071</v>
+        <v>33.25964872447344</v>
       </c>
       <c r="C4" t="n">
-        <v>142.049075327471</v>
+        <v>113.6392602619768</v>
       </c>
       <c r="D4" t="n">
-        <v>131.0603732738365</v>
+        <v>169.2336692580652</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.00497515844602</v>
+        <v>34.60660657470007</v>
       </c>
       <c r="C5" t="n">
-        <v>168.4924497413589</v>
+        <v>137.9600961392831</v>
       </c>
       <c r="D5" t="n">
-        <v>87.645526296634</v>
+        <v>101.6108873895449</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.54471541160352</v>
+        <v>34.21390749300134</v>
       </c>
       <c r="C6" t="n">
-        <v>152.1512592041707</v>
+        <v>122.8480537278119</v>
       </c>
       <c r="D6" t="n">
-        <v>41.0164373357275</v>
+        <v>41.861722109084</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>140.9730798436165</v>
+        <v>102.2264432001076</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>100.8893028269235</v>
+        <v>68.59471209572465</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>49.69999577979051</v>
+        <v>39.2718716652809</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.09683316982194</v>
+        <v>4.043818793792612</v>
       </c>
       <c r="C2" t="n">
-        <v>12.49273953654066</v>
+        <v>2.667408512438584</v>
       </c>
       <c r="D2" t="n">
-        <v>21.2833084803666</v>
+        <v>25.67368421375834</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24716374175872</v>
+        <v>18.34395585385165</v>
       </c>
       <c r="C3" t="n">
-        <v>32.0736974977433</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D3" t="n">
-        <v>85.55931242510952</v>
+        <v>117.2255846255904</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.14777054391831</v>
+        <v>38.78590655167874</v>
       </c>
       <c r="C4" t="n">
-        <v>130.5626271877833</v>
+        <v>101.7954559579433</v>
       </c>
       <c r="D4" t="n">
-        <v>141.6151428421939</v>
+        <v>189.973089510279</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.63177216211199</v>
+        <v>41.47884050442774</v>
       </c>
       <c r="C5" t="n">
-        <v>213.8246499849554</v>
+        <v>172.1985473248906</v>
       </c>
       <c r="D5" t="n">
-        <v>110.2257234943107</v>
+        <v>132.8795517698058</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.30070220160257</v>
+        <v>39.84913931537804</v>
       </c>
       <c r="C6" t="n">
-        <v>203.1903588525539</v>
+        <v>168.5336831449372</v>
       </c>
       <c r="D6" t="n">
-        <v>55.2655235151657</v>
+        <v>59.25043744670351</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.99645822427728</v>
+        <v>27.66761380108361</v>
       </c>
       <c r="C7" t="n">
-        <v>177.4440253086812</v>
+        <v>136.122264436933</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>138.274255404642</v>
+        <v>98.88653751025997</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>79.87499321752047</v>
+        <v>59.3515574602409</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>37.5813021185679</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.471058971589222</v>
+        <v>2.436697801940583</v>
       </c>
       <c r="C2" t="n">
-        <v>6.150649367106268</v>
+        <v>1.2772537632251</v>
       </c>
       <c r="D2" t="n">
-        <v>14.84598878362027</v>
+        <v>17.8982423961236</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.01645303126072</v>
+        <v>18.12306262039612</v>
       </c>
       <c r="C3" t="n">
-        <v>40.42346172236242</v>
+        <v>18.89373456822987</v>
       </c>
       <c r="D3" t="n">
-        <v>86.62941742273856</v>
+        <v>115.7578718077414</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.2746369819444</v>
+        <v>42.51262083699963</v>
       </c>
       <c r="C4" t="n">
-        <v>127.1422181861874</v>
+        <v>95.78421476484006</v>
       </c>
       <c r="D4" t="n">
-        <v>151.4041492012389</v>
+        <v>203.8972171996116</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.3680829402971</v>
+        <v>43.07418052382881</v>
       </c>
       <c r="C5" t="n">
-        <v>254.6162670964103</v>
+        <v>202.534551386117</v>
       </c>
       <c r="D5" t="n">
-        <v>112.8764422957771</v>
+        <v>140.6844460185679</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.97490083251287</v>
+        <v>33.00635781677777</v>
       </c>
       <c r="C6" t="n">
-        <v>234.1841338756257</v>
+        <v>198.3601601476596</v>
       </c>
       <c r="D6" t="n">
-        <v>53.41394734495622</v>
+        <v>57.43911293236815</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>182.0552942755285</v>
+        <v>137.3199966361141</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>98.13550051651117</v>
+        <v>73.76852249710534</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>28.6218725696115</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.36890045708532</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.561379760379928</v>
+        <v>2.625193361155971</v>
       </c>
       <c r="C2" t="n">
-        <v>6.852598975642736</v>
+        <v>1.831941216124548</v>
       </c>
       <c r="D2" t="n">
-        <v>18.30861293649877</v>
+        <v>17.61157206648353</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.05862712481433</v>
+        <v>13.46957850226624</v>
       </c>
       <c r="C3" t="n">
-        <v>32.37313054753857</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D3" t="n">
-        <v>79.35466693426969</v>
+        <v>105.513334513926</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.78590655167874</v>
+        <v>38.79866927183395</v>
       </c>
       <c r="C4" t="n">
-        <v>115.7706345278966</v>
+        <v>72.28804695910115</v>
       </c>
       <c r="D4" t="n">
-        <v>158.1301027230338</v>
+        <v>212.6013923454638</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.44924920458011</v>
+        <v>51.8362787842316</v>
       </c>
       <c r="C5" t="n">
-        <v>247.4740525480148</v>
+        <v>192.152569413707</v>
       </c>
       <c r="D5" t="n">
-        <v>136.1929502716388</v>
+        <v>172.5912464065893</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.27303333943441</v>
+        <v>42.78751019418875</v>
       </c>
       <c r="C6" t="n">
-        <v>306.6371144490403</v>
+        <v>253.7464386304476</v>
       </c>
       <c r="D6" t="n">
-        <v>69.15234479173684</v>
+        <v>79.98004022187492</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.97165248976386</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="C7" t="n">
-        <v>245.7147606620044</v>
+        <v>201.7579889520577</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>154.2963779379499</v>
+        <v>116.6610796956485</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>62.12499472473814</v>
+        <v>51.14218315732908</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.745547418150829</v>
+        <v>1.858448404139212</v>
       </c>
       <c r="C2" t="n">
-        <v>4.074252972624263</v>
+        <v>1.799543541884403</v>
       </c>
       <c r="D2" t="n">
-        <v>12.9571062006494</v>
+        <v>13.5422278323805</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.00186568441726</v>
+        <v>11.71715885018568</v>
       </c>
       <c r="C3" t="n">
-        <v>30.46854000129976</v>
+        <v>9.979465413668827</v>
       </c>
       <c r="D3" t="n">
-        <v>76.52723354603887</v>
+        <v>98.69018796941062</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.14853130744431</v>
+        <v>34.43381897875263</v>
       </c>
       <c r="C4" t="n">
-        <v>103.7481521416902</v>
+        <v>55.9262397201238</v>
       </c>
       <c r="D4" t="n">
-        <v>160.8485621160932</v>
+        <v>215.8814114253524</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.98983233672161</v>
+        <v>56.13142499031139</v>
       </c>
       <c r="C5" t="n">
-        <v>243.473430653209</v>
+        <v>176.6409556866074</v>
       </c>
       <c r="D5" t="n">
-        <v>152.3917873917112</v>
+        <v>193.9442589739574</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.7070068824405</v>
+        <v>49.95230493978197</v>
       </c>
       <c r="C6" t="n">
-        <v>347.371790193649</v>
+        <v>282.7678825156876</v>
       </c>
       <c r="D6" t="n">
-        <v>81.50960314509145</v>
+        <v>98.89831848271095</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.35471402086936</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>307.8171751895449</v>
+        <v>256.8536701143888</v>
       </c>
       <c r="D7" t="n">
-        <v>45.15450390912779</v>
+        <v>46.59178254814513</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>194.9358241552466</v>
+        <v>152.9612010601743</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>66.22968187619405</v>
+        <v>58.90780749792134</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.589269606726339</v>
+        <v>2.962914571416874</v>
       </c>
       <c r="C2" t="n">
-        <v>14.6830186647153</v>
+        <v>10.389835954044</v>
       </c>
       <c r="D2" t="n">
-        <v>15.81202852459913</v>
+        <v>20.6373184909722</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.223519681398782</v>
+        <v>9.164614819143976</v>
       </c>
       <c r="C3" t="n">
-        <v>23.93500902953724</v>
+        <v>8.62465358180823</v>
       </c>
       <c r="D3" t="n">
-        <v>70.43548904118741</v>
+        <v>88.65181769348698</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.43083267791088</v>
+        <v>28.72888306937441</v>
       </c>
       <c r="C4" t="n">
-        <v>91.92987327796708</v>
+        <v>41.84895938892878</v>
       </c>
       <c r="D4" t="n">
-        <v>161.0782910788869</v>
+        <v>215.1794618168159</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.59713325502288</v>
+        <v>54.38882281527331</v>
       </c>
       <c r="C5" t="n">
-        <v>221.9486122375977</v>
+        <v>145.1023106876786</v>
       </c>
       <c r="D5" t="n">
-        <v>167.3388961888689</v>
+        <v>217.7761844945488</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.44790760397736</v>
+        <v>59.57245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>363.0699359845555</v>
+        <v>285.7867567062465</v>
       </c>
       <c r="D6" t="n">
-        <v>99.05932510620744</v>
+        <v>124.9813914891402</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>30.48228446915921</v>
       </c>
       <c r="C7" t="n">
-        <v>379.3816740906161</v>
+        <v>316.1414139738536</v>
       </c>
       <c r="D7" t="n">
-        <v>53.59851591335461</v>
+        <v>57.9103518304066</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.759332943739289</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>272.376083066235</v>
+        <v>223.1414356982575</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>122.9187395625176</v>
+        <v>106.1671784849543</v>
       </c>
       <c r="D9" t="n">
         <v>33.05937219280708</v>
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>46.12250714551515</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.275511251994859</v>
+        <v>6.083890523217484</v>
       </c>
       <c r="C2" t="n">
-        <v>10.62545540306323</v>
+        <v>4.003567137918493</v>
       </c>
       <c r="D2" t="n">
-        <v>14.1734916062112</v>
+        <v>8.992808970900782</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.648755306057895</v>
+        <v>2.143155238370787</v>
       </c>
       <c r="C2" t="n">
-        <v>8.809222150206629</v>
+        <v>5.983752257384309</v>
       </c>
       <c r="D2" t="n">
-        <v>11.89092819383737</v>
+        <v>15.35453409442012</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.86089492563322</v>
+        <v>12.56637061435917</v>
       </c>
       <c r="C3" t="n">
-        <v>36.72718161587317</v>
+        <v>19.08517537055799</v>
       </c>
       <c r="D3" t="n">
-        <v>76.16889563398878</v>
+        <v>96.44198572668542</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.30467025014855</v>
+        <v>40.77689089589127</v>
       </c>
       <c r="C4" t="n">
-        <v>130.5498644676281</v>
+        <v>66.22575488537709</v>
       </c>
       <c r="D4" t="n">
-        <v>163.9754285541193</v>
+        <v>219.289057706793</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.52606220522283</v>
+        <v>34.55751918948773</v>
       </c>
       <c r="C5" t="n">
-        <v>316.4172850787471</v>
+        <v>231.643370817035</v>
       </c>
       <c r="D5" t="n">
-        <v>149.053845197272</v>
+        <v>194.1406085148068</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.33588088803943</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="C6" t="n">
-        <v>310.3805184453334</v>
+        <v>261.4345049024045</v>
       </c>
       <c r="D6" t="n">
-        <v>78.61148392215486</v>
+        <v>94.3901330248096</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.431609136970102</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>191.5173786490593</v>
+        <v>156.9029180927252</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>90.54168202416209</v>
+        <v>78.1912959047372</v>
       </c>
       <c r="D8" t="n">
         <v>24.36697801940583</v>
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.16718451382499</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>19.74687332322034</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.9264920953685</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.425538724295373</v>
+        <v>6.624833508257476</v>
       </c>
       <c r="C2" t="n">
-        <v>5.813909904549611</v>
+        <v>5.563564239966674</v>
       </c>
       <c r="D2" t="n">
-        <v>22.85803179797848</v>
+        <v>10.98575681052181</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.090983741325465</v>
+        <v>12.92470852640926</v>
       </c>
       <c r="C3" t="n">
-        <v>26.77225989481052</v>
+        <v>10.08745766113598</v>
       </c>
       <c r="D3" t="n">
-        <v>15.04037482906113</v>
+        <v>10.69123249924777</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39701191497396</v>
+        <v>13.39872693348748</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13729767251073</v>
+        <v>70.1462762988462</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576119048820465</v>
+        <v>1.576320815704409</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.586725274241098</v>
+        <v>4.524875168873549</v>
       </c>
       <c r="C2" t="n">
-        <v>5.567491230783661</v>
+        <v>5.393721887131976</v>
       </c>
       <c r="D2" t="n">
-        <v>30.51664563880786</v>
+        <v>27.15710499487527</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.90078672860884</v>
+        <v>18.90846078379357</v>
       </c>
       <c r="C3" t="n">
-        <v>24.20498964820511</v>
+        <v>17.47510913559323</v>
       </c>
       <c r="D3" t="n">
-        <v>30.60598467989431</v>
+        <v>17.33275571847744</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.70792221021996</v>
+        <v>15.02172162268045</v>
       </c>
       <c r="C4" t="n">
-        <v>41.33845058272045</v>
+        <v>16.15760371649401</v>
       </c>
       <c r="D4" t="n">
-        <v>22.94737083906494</v>
+        <v>20.67560665143782</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43677813493533</v>
+        <v>15.44421849143824</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12097275279713</v>
+        <v>86.16248211012912</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249848028407439</v>
+        <v>3.251414419250156</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.672137324510571</v>
+        <v>4.557272843113694</v>
       </c>
       <c r="C2" t="n">
-        <v>9.867546175384691</v>
+        <v>5.253331965424683</v>
       </c>
       <c r="D2" t="n">
-        <v>23.24974913197296</v>
+        <v>41.15191851891355</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.47372647726148</v>
+        <v>17.0824100538945</v>
       </c>
       <c r="C3" t="n">
-        <v>22.67346322958009</v>
+        <v>19.6055016538088</v>
       </c>
       <c r="D3" t="n">
-        <v>47.91419670576558</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.79421819720244</v>
+        <v>27.17183121043897</v>
       </c>
       <c r="C4" t="n">
-        <v>52.4930679983727</v>
+        <v>32.39178375391926</v>
       </c>
       <c r="D4" t="n">
-        <v>33.11925880276615</v>
+        <v>24.72138894063893</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.792933349861935</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="C5" t="n">
-        <v>45.11130701014094</v>
+        <v>19.26679869584366</v>
       </c>
       <c r="D5" t="n">
-        <v>30.90050899116836</v>
+        <v>29.86967390170921</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
         <v>31.45225120095506</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72388773485946</v>
+        <v>16.74032089860937</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0157151826427</v>
+        <v>102.1159574815171</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180971933714866</v>
+        <v>5.02209626958281</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.430627389265855</v>
+        <v>5.957245069369645</v>
       </c>
       <c r="C2" t="n">
-        <v>6.766205177669017</v>
+        <v>6.571819132228149</v>
       </c>
       <c r="D2" t="n">
-        <v>25.96428153421539</v>
+        <v>43.01625740927824</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1742934274662</v>
+        <v>16.27737693641212</v>
       </c>
       <c r="C3" t="n">
-        <v>31.49937509075891</v>
+        <v>20.04728812071987</v>
       </c>
       <c r="D3" t="n">
-        <v>54.92387531408781</v>
+        <v>58.51707191163113</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.46537377400877</v>
+        <v>30.51566389110361</v>
       </c>
       <c r="C4" t="n">
-        <v>54.30537426041231</v>
+        <v>41.69580674706629</v>
       </c>
       <c r="D4" t="n">
-        <v>48.79187915336223</v>
+        <v>36.06744715861932</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.94206118991621</v>
+        <v>26.92443078896878</v>
       </c>
       <c r="C5" t="n">
-        <v>73.11566027378122</v>
+        <v>40.96342295969817</v>
       </c>
       <c r="D5" t="n">
-        <v>35.31837366027901</v>
+        <v>31.71045084717198</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.539642442166258</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>42.9082651618111</v>
+        <v>21.89690079552086</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04075083282312</v>
+        <v>18.06756046086043</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6944220998461</v>
+        <v>117.8693230065657</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013583610941041</v>
+        <v>6.882880175565878</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.841799750896022</v>
+        <v>5.622469102221483</v>
       </c>
       <c r="C2" t="n">
-        <v>10.79529775589793</v>
+        <v>12.51924672455533</v>
       </c>
       <c r="D2" t="n">
-        <v>22.13644723535708</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.82791641431632</v>
+        <v>16.56208377064369</v>
       </c>
       <c r="C3" t="n">
-        <v>26.78207737185298</v>
+        <v>21.78498155723672</v>
       </c>
       <c r="D3" t="n">
-        <v>58.74778262212914</v>
+        <v>73.55744674069227</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.28821721888784</v>
+        <v>22.46238747316702</v>
       </c>
       <c r="C4" t="n">
-        <v>56.65371476897069</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="D4" t="n">
-        <v>56.23254500384881</v>
+        <v>49.0471335564664</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.21771131063132</v>
+        <v>22.48202242725196</v>
       </c>
       <c r="C5" t="n">
-        <v>64.37810570598461</v>
+        <v>44.52225838759286</v>
       </c>
       <c r="D5" t="n">
-        <v>35.63744166415923</v>
+        <v>29.91876128692155</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.70694046251572</v>
+        <v>13.16229147083699</v>
       </c>
       <c r="C6" t="n">
-        <v>54.50074205355744</v>
+        <v>30.10823859384119</v>
       </c>
       <c r="D6" t="n">
-        <v>31.79880814055419</v>
+        <v>30.87302005544945</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>26.35010838198439</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.047030235502042</v>
+        <v>7.061709585901287</v>
       </c>
       <c r="C21" t="n">
-        <v>66.06590845783164</v>
+        <v>66.20352736782456</v>
       </c>
       <c r="D21" t="n">
-        <v>4.404393897188776</v>
+        <v>5.296282189425965</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.886559234663874</v>
+        <v>6.218389958699297</v>
       </c>
       <c r="C2" t="n">
-        <v>11.53553552490002</v>
+        <v>5.619523859108742</v>
       </c>
       <c r="D2" t="n">
-        <v>23.66110142005238</v>
+        <v>35.41556668299944</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.88529974951915</v>
+        <v>18.55012287174348</v>
       </c>
       <c r="C3" t="n">
-        <v>36.54064955206628</v>
+        <v>39.28463438543612</v>
       </c>
       <c r="D3" t="n">
-        <v>63.14601233715484</v>
+        <v>85.05862109594365</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.98940606389831</v>
+        <v>28.81822211046087</v>
       </c>
       <c r="C4" t="n">
-        <v>63.18822748843746</v>
+        <v>48.80464187351743</v>
       </c>
       <c r="D4" t="n">
-        <v>73.97272601958868</v>
+        <v>75.74674412116265</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.48264432205772</v>
+        <v>29.35425635697964</v>
       </c>
       <c r="C5" t="n">
-        <v>88.08731276354507</v>
+        <v>60.84381397069608</v>
       </c>
       <c r="D5" t="n">
-        <v>48.13018120069989</v>
+        <v>41.96971435655115</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.48180144307371</v>
+        <v>22.98369550412208</v>
       </c>
       <c r="C6" t="n">
-        <v>82.75740447718914</v>
+        <v>54.42023874180921</v>
       </c>
       <c r="D6" t="n">
-        <v>36.4277485660779</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>11.49822911213864</v>
       </c>
       <c r="C7" t="n">
-        <v>56.89227946110266</v>
+        <v>32.75797564760332</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>28.28906009787184</v>
+        <v>21.36283004441059</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.264767261013784</v>
+        <v>7.284023723618187</v>
       </c>
       <c r="C21" t="n">
-        <v>75.37196033301801</v>
+        <v>75.57174613253869</v>
       </c>
       <c r="D21" t="n">
-        <v>5.448575445760338</v>
+        <v>6.373520758165913</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.822344723260333</v>
+        <v>5.721625620350411</v>
       </c>
       <c r="C2" t="n">
-        <v>8.139670215910305</v>
+        <v>6.46677212787374</v>
       </c>
       <c r="D2" t="n">
-        <v>20.72862102746715</v>
+        <v>41.91473648511332</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.11110172149591</v>
+        <v>20.24363766156923</v>
       </c>
       <c r="C3" t="n">
-        <v>41.38066573400306</v>
+        <v>28.72102908774044</v>
       </c>
       <c r="D3" t="n">
-        <v>67.08282063118456</v>
+        <v>93.65382224662449</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.63427543686822</v>
+        <v>33.14478424307656</v>
       </c>
       <c r="C4" t="n">
-        <v>78.66940703670541</v>
+        <v>77.99298286847934</v>
       </c>
       <c r="D4" t="n">
-        <v>87.46292122364409</v>
+        <v>101.3615234726662</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.2749557771139</v>
+        <v>36.81553890925539</v>
       </c>
       <c r="C5" t="n">
-        <v>104.212518805799</v>
+        <v>77.63169971331654</v>
       </c>
       <c r="D5" t="n">
-        <v>63.81360077604268</v>
+        <v>59.19938656608268</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29691407950582</v>
+        <v>32.32207966691774</v>
       </c>
       <c r="C6" t="n">
-        <v>113.7914311561351</v>
+        <v>77.72594749292425</v>
       </c>
       <c r="D6" t="n">
-        <v>42.9082651618111</v>
+        <v>39.7686360036298</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>90.00957476846031</v>
+        <v>57.43125895073415</v>
       </c>
       <c r="D7" t="n">
-        <v>36.89015173477814</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>53.7408693304704</v>
+        <v>33.71321616383547</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.06405994715006</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.468245564940403</v>
+        <v>7.493087598475137</v>
       </c>
       <c r="C21" t="n">
-        <v>84.01776260557953</v>
+        <v>85.23387143265468</v>
       </c>
       <c r="D21" t="n">
-        <v>6.534714869322853</v>
+        <v>7.493087598475137</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_52_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497608357739</v>
+        <v>10.84497630435789</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907107553724</v>
+        <v>37.78907184484182</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.404521111878692</v>
+        <v>5.931719629059228</v>
       </c>
       <c r="C2" t="n">
-        <v>8.262388678941157</v>
+        <v>14.82635382953533</v>
       </c>
       <c r="D2" t="n">
-        <v>39.78238047148925</v>
+        <v>27.55078582427824</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.78221624057323</v>
+        <v>16.66516727958961</v>
       </c>
       <c r="C3" t="n">
-        <v>26.64954143177967</v>
+        <v>24.93639168786898</v>
       </c>
       <c r="D3" t="n">
-        <v>103.89835954044</v>
+        <v>62.29189183446012</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.27165068110266</v>
+        <v>33.97436105316512</v>
       </c>
       <c r="C4" t="n">
-        <v>74.64915018781471</v>
+        <v>60.76331065894783</v>
       </c>
       <c r="D4" t="n">
-        <v>121.8584520419311</v>
+        <v>83.21293541195965</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.07418052382881</v>
+        <v>43.51596699073988</v>
       </c>
       <c r="C5" t="n">
-        <v>111.3792770468007</v>
+        <v>88.52909923045614</v>
       </c>
       <c r="D5" t="n">
-        <v>80.84692344472485</v>
+        <v>63.81360077604268</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.0164373357275</v>
+        <v>41.45920555034281</v>
       </c>
       <c r="C6" t="n">
-        <v>101.1524112116616</v>
+        <v>106.7876430340383</v>
       </c>
       <c r="D6" t="n">
-        <v>48.18123208132072</v>
+        <v>47.57745724320893</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.40432548989622</v>
+        <v>30.42239785920016</v>
       </c>
       <c r="C7" t="n">
-        <v>85.33841919165398</v>
+        <v>110.6105685943754</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.43798264928109</v>
+        <v>16.02212253330794</v>
       </c>
       <c r="C8" t="n">
-        <v>54.65880343394117</v>
+        <v>79.77681844709581</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>44.26405874137593</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.68655316963059</v>
+        <v>7.692431537298059</v>
       </c>
       <c r="C21" t="n">
-        <v>94.16027632797471</v>
+        <v>94.23228633190121</v>
       </c>
       <c r="D21" t="n">
-        <v>8.647372315834414</v>
+        <v>7.692431537298059</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.712789891012189</v>
+        <v>7.576147033672636</v>
       </c>
       <c r="C2" t="n">
-        <v>9.814531799355363</v>
+        <v>17.68127615348505</v>
       </c>
       <c r="D2" t="n">
-        <v>44.07261793904782</v>
+        <v>28.15063367157304</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.80537727484765</v>
+        <v>18.19669369821463</v>
       </c>
       <c r="C3" t="n">
-        <v>29.24135537099124</v>
+        <v>41.97462309507238</v>
       </c>
       <c r="D3" t="n">
-        <v>109.8379331511331</v>
+        <v>68.36400138522664</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.50137964389641</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="C4" t="n">
-        <v>69.85036740945631</v>
+        <v>61.49078570779472</v>
       </c>
       <c r="D4" t="n">
-        <v>142.3426178910408</v>
+        <v>92.73392464774521</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.42470551197393</v>
+        <v>46.92754026299754</v>
       </c>
       <c r="C5" t="n">
-        <v>123.8720165833413</v>
+        <v>99.15651812892787</v>
       </c>
       <c r="D5" t="n">
-        <v>101.1691009226338</v>
+        <v>77.55806863549803</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.66425195181016</v>
+        <v>50.11331156327844</v>
       </c>
       <c r="C6" t="n">
-        <v>135.1650604252924</v>
+        <v>123.4115769100496</v>
       </c>
       <c r="D6" t="n">
-        <v>60.49823877880121</v>
+        <v>55.2252718592916</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.20765715387736</v>
+        <v>39.34550274309942</v>
       </c>
       <c r="C7" t="n">
-        <v>114.0241053620415</v>
+        <v>131.2115624202904</v>
       </c>
       <c r="D7" t="n">
-        <v>43.11835917051991</v>
+        <v>44.13643153982385</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.86490403190821</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="C8" t="n">
-        <v>81.11199532487147</v>
+        <v>112.4886519525995</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.42656152972862</v>
+        <v>11.87031149204818</v>
       </c>
       <c r="C9" t="n">
-        <v>50.03280825153018</v>
+        <v>69.77968157475051</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>34.73423377625215</v>
+        <v>41.56719779780995</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.864209621818022</v>
+        <v>7.876204058266429</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2347250836343</v>
+        <v>103.3751782647469</v>
       </c>
       <c r="D21" t="n">
-        <v>9.830262027272527</v>
+        <v>8.860729565549732</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.003788122096745</v>
+        <v>8.659996499161114</v>
       </c>
       <c r="C2" t="n">
-        <v>8.686503687175778</v>
+        <v>11.96946801017711</v>
       </c>
       <c r="D2" t="n">
-        <v>43.76631265532281</v>
+        <v>25.86021627756523</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.54521413322225</v>
+        <v>21.42664364518664</v>
       </c>
       <c r="C3" t="n">
-        <v>33.10453258720245</v>
+        <v>54.29064804484862</v>
       </c>
       <c r="D3" t="n">
-        <v>116.0671223345792</v>
+        <v>73.14511270490861</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.31444666946201</v>
+        <v>32.80019079888594</v>
       </c>
       <c r="C4" t="n">
-        <v>71.06282582420111</v>
+        <v>80.66039138091794</v>
       </c>
       <c r="D4" t="n">
-        <v>157.2622377524796</v>
+        <v>102.9696262122225</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.60909415392309</v>
+        <v>47.49204519293946</v>
       </c>
       <c r="C5" t="n">
-        <v>124.4119778206771</v>
+        <v>105.3415286656828</v>
       </c>
       <c r="D5" t="n">
-        <v>122.9393562643069</v>
+        <v>88.94634200476104</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.34602682691394</v>
+        <v>55.6680400739069</v>
       </c>
       <c r="C6" t="n">
-        <v>160.0405837554981</v>
+        <v>137.2581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>73.258013690897</v>
+        <v>64.84541761320608</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.35223610830891</v>
+        <v>48.08894779712151</v>
       </c>
       <c r="C7" t="n">
-        <v>148.9379989681709</v>
+        <v>151.3933499764921</v>
       </c>
       <c r="D7" t="n">
-        <v>49.10702016642545</v>
+        <v>48.44826745687584</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.79251674370121</v>
+        <v>32.21114217633784</v>
       </c>
       <c r="C8" t="n">
-        <v>109.9851953067702</v>
+        <v>140.6942634956104</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>40.97324043674063</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.08593613408398</v>
+        <v>16.9734360587231</v>
       </c>
       <c r="C9" t="n">
-        <v>70.9999939711293</v>
+        <v>99.51092905016091</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>59.36137493728339</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.53926689373453</v>
+        <v>39.09319358310798</v>
       </c>
       <c r="D11" t="n">
         <v>36.96083756948391</v>
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1562,7 +1562,7 @@
         <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.025262478309028</v>
+        <v>8.043598413473706</v>
       </c>
       <c r="C21" t="n">
-        <v>110.3473590767491</v>
+        <v>111.6049279869477</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03473590767491</v>
+        <v>10.05449801684213</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.433392705929348</v>
+        <v>7.849072895453248</v>
       </c>
       <c r="C2" t="n">
-        <v>5.975898275750335</v>
+        <v>8.138688468206057</v>
       </c>
       <c r="D2" t="n">
-        <v>36.12635202087413</v>
+        <v>21.24894731071796</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.26251185212817</v>
+        <v>24.43570035870311</v>
       </c>
       <c r="C3" t="n">
-        <v>47.92401418280805</v>
+        <v>71.80502708861171</v>
       </c>
       <c r="D3" t="n">
-        <v>124.431612774762</v>
+        <v>79.19267856306897</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.31298189567226</v>
+        <v>22.80698091735765</v>
       </c>
       <c r="C4" t="n">
-        <v>100.9914045881651</v>
+        <v>97.494419265638</v>
       </c>
       <c r="D4" t="n">
-        <v>146.8478581058294</v>
+        <v>100.1745904982318</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.17048960983623</v>
+        <v>31.34229545807943</v>
       </c>
       <c r="C5" t="n">
-        <v>95.62222639363934</v>
+        <v>82.00047699721485</v>
       </c>
       <c r="D5" t="n">
-        <v>76.82175785731292</v>
+        <v>62.63550353094652</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.77993394999525</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C6" t="n">
-        <v>98.09328536522857</v>
+        <v>99.70335160019334</v>
       </c>
       <c r="D6" t="n">
-        <v>32.32207966691774</v>
+        <v>31.87931145230244</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>77.31361345714056</v>
+        <v>98.93267965235957</v>
       </c>
       <c r="D7" t="n">
-        <v>28.14670668075605</v>
+        <v>28.80545939030566</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>52.32224389783376</v>
+        <v>73.35127972280043</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>45.26249615659493</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
         <v>28.89774367450487</v>
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>28.60910984945629</v>
@@ -1859,7 +1859,7 @@
         <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.927972564691488</v>
+        <v>4.728096943652639</v>
       </c>
       <c r="C2" t="n">
-        <v>2.569233742013903</v>
+        <v>3.771874679716245</v>
       </c>
       <c r="D2" t="n">
-        <v>24.63401339496097</v>
+        <v>14.42776426161113</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.37050409959532</v>
+        <v>26.29611225825082</v>
       </c>
       <c r="C3" t="n">
-        <v>36.11358930071892</v>
+        <v>52.0817157102933</v>
       </c>
       <c r="D3" t="n">
-        <v>126.1005838719816</v>
+        <v>78.30910562924683</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.25964872447344</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C4" t="n">
-        <v>113.6392602619768</v>
+        <v>141.1684476367616</v>
       </c>
       <c r="D4" t="n">
-        <v>169.2336692580652</v>
+        <v>115.2856511619987</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.60660657470007</v>
+        <v>34.23845118560752</v>
       </c>
       <c r="C5" t="n">
-        <v>137.9600961392831</v>
+        <v>127.7744637077224</v>
       </c>
       <c r="D5" t="n">
-        <v>101.6108873895449</v>
+        <v>78.14711725804612</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.21390749300134</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>122.8480537278119</v>
+        <v>116.810305346694</v>
       </c>
       <c r="D6" t="n">
-        <v>41.861722109084</v>
+        <v>39.20511282139213</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="C7" t="n">
-        <v>102.2264432001076</v>
+        <v>121.1506119471691</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>68.59471209572465</v>
+        <v>94.29686699290613</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>39.2718716652809</v>
+        <v>51.58593311964863</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.043818793792612</v>
+        <v>4.841979677345269</v>
       </c>
       <c r="C2" t="n">
-        <v>2.667408512438584</v>
+        <v>5.134540493210818</v>
       </c>
       <c r="D2" t="n">
-        <v>25.67368421375834</v>
+        <v>11.08196808553799</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.34395585385165</v>
+        <v>21.34810382884689</v>
       </c>
       <c r="C3" t="n">
-        <v>22.57528845915541</v>
+        <v>32.34367811641117</v>
       </c>
       <c r="D3" t="n">
-        <v>117.2255846255904</v>
+        <v>72.20754364735291</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.78590655167874</v>
+        <v>41.00661985868502</v>
       </c>
       <c r="C4" t="n">
-        <v>101.7954559579433</v>
+        <v>135.4124608467626</v>
       </c>
       <c r="D4" t="n">
-        <v>189.973089510279</v>
+        <v>126.1850141745468</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.47884050442774</v>
+        <v>41.30703465618456</v>
       </c>
       <c r="C5" t="n">
-        <v>172.1985473248906</v>
+        <v>192.6925306510427</v>
       </c>
       <c r="D5" t="n">
-        <v>132.8795517698058</v>
+        <v>97.80661503558851</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.84913931537804</v>
+        <v>41.05668899160162</v>
       </c>
       <c r="C6" t="n">
-        <v>168.5336831449372</v>
+        <v>158.6317757999039</v>
       </c>
       <c r="D6" t="n">
-        <v>59.25043744670351</v>
+        <v>51.4818678629985</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.66761380108361</v>
+        <v>28.80545939030566</v>
       </c>
       <c r="C7" t="n">
-        <v>136.122264436933</v>
+        <v>144.9854827108732</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>98.88653751025997</v>
+        <v>125.0893837366073</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>59.3515574602409</v>
+        <v>79.5421807457808</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>37.5813021185679</v>
+        <v>45.12603322570465</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.436697801940583</v>
+        <v>2.869648539513427</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2772537632251</v>
+        <v>2.393500902953724</v>
       </c>
       <c r="D2" t="n">
-        <v>17.8982423961236</v>
+        <v>7.750898125028567</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.12306262039612</v>
+        <v>21.4364611222291</v>
       </c>
       <c r="C3" t="n">
-        <v>18.89373456822987</v>
+        <v>29.11863690796039</v>
       </c>
       <c r="D3" t="n">
-        <v>115.7578718077414</v>
+        <v>68.84014902178635</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.51262083699963</v>
+        <v>45.05240214788613</v>
       </c>
       <c r="C4" t="n">
-        <v>95.78421476484006</v>
+        <v>128.8396599668302</v>
       </c>
       <c r="D4" t="n">
-        <v>203.8972171996116</v>
+        <v>134.2000024320178</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.07418052382881</v>
+        <v>43.46687960552754</v>
       </c>
       <c r="C5" t="n">
-        <v>202.534551386117</v>
+        <v>236.404847182632</v>
       </c>
       <c r="D5" t="n">
-        <v>140.6844460185679</v>
+        <v>103.3044021793706</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.00635781677777</v>
+        <v>34.57617239586842</v>
       </c>
       <c r="C6" t="n">
-        <v>198.3601601476596</v>
+        <v>192.8054316370311</v>
       </c>
       <c r="D6" t="n">
-        <v>57.43911293236815</v>
+        <v>50.59633143376788</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.803331663981149</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>137.3199966361141</v>
+        <v>155.8848457234213</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>73.76852249710534</v>
+        <v>96.63342652901355</v>
       </c>
       <c r="D8" t="n">
         <v>31.46010518258904</v>
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.625193361155971</v>
+        <v>3.463605900582747</v>
       </c>
       <c r="C2" t="n">
-        <v>1.831941216124548</v>
+        <v>9.512153506447346</v>
       </c>
       <c r="D2" t="n">
-        <v>17.61157206648353</v>
+        <v>9.852819959820989</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.46957850226624</v>
+        <v>15.84540794654352</v>
       </c>
       <c r="C3" t="n">
-        <v>11.93314334511998</v>
+        <v>19.04099672386689</v>
       </c>
       <c r="D3" t="n">
-        <v>105.513334513926</v>
+        <v>60.78000036992003</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.79866927183395</v>
+        <v>43.45706212848506</v>
       </c>
       <c r="C4" t="n">
-        <v>72.28804695910115</v>
+        <v>102.3953038052381</v>
       </c>
       <c r="D4" t="n">
-        <v>212.6013923454638</v>
+        <v>136.9950381460084</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.8362787842316</v>
+        <v>53.52979357405735</v>
       </c>
       <c r="C5" t="n">
-        <v>192.152569413707</v>
+        <v>236.5030219530567</v>
       </c>
       <c r="D5" t="n">
-        <v>172.5912464065893</v>
+        <v>122.4484824121835</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.78751019418875</v>
+        <v>43.71329827929349</v>
       </c>
       <c r="C6" t="n">
-        <v>253.7464386304476</v>
+        <v>277.1326506933109</v>
       </c>
       <c r="D6" t="n">
-        <v>79.98004022187492</v>
+        <v>65.89196066593318</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>201.7579889520577</v>
+        <v>208.6449490973491</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>116.6610796956485</v>
+        <v>142.196337483108</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>51.14218315732908</v>
+        <v>65.78593191387449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
         <v>24.76949457814703</v>
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.858448404139212</v>
+        <v>2.398409641474958</v>
       </c>
       <c r="C2" t="n">
-        <v>1.799543541884403</v>
+        <v>4.953898915629405</v>
       </c>
       <c r="D2" t="n">
-        <v>13.5422278323805</v>
+        <v>8.244717220264713</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.71715885018568</v>
+        <v>14.29915531235479</v>
       </c>
       <c r="C3" t="n">
-        <v>9.979465413668827</v>
+        <v>27.34167356327367</v>
       </c>
       <c r="D3" t="n">
-        <v>98.69018796941062</v>
+        <v>56.67138622764713</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.43381897875263</v>
+        <v>39.39851711912875</v>
       </c>
       <c r="C4" t="n">
-        <v>55.9262397201238</v>
+        <v>81.88561251581795</v>
       </c>
       <c r="D4" t="n">
-        <v>215.8814114253524</v>
+        <v>136.7653091832146</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.13142499031139</v>
+        <v>59.17484287347651</v>
       </c>
       <c r="C5" t="n">
-        <v>176.6409556866074</v>
+        <v>226.5873701401639</v>
       </c>
       <c r="D5" t="n">
-        <v>193.9442589739574</v>
+        <v>134.7694161004809</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.95230493978197</v>
+        <v>51.07935130425731</v>
       </c>
       <c r="C6" t="n">
-        <v>282.7678825156876</v>
+        <v>321.8119887135833</v>
       </c>
       <c r="D6" t="n">
-        <v>98.89831848271095</v>
+        <v>78.69198723390311</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>17.78632315783946</v>
       </c>
       <c r="C7" t="n">
-        <v>256.8536701143888</v>
+        <v>270.7473636248896</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>44.19631814978291</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>152.9612010601743</v>
+        <v>178.9137016219387</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>58.90780749792134</v>
+        <v>73.99530621678632</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.36962016288231</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.06233313145306</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.962914571416874</v>
+        <v>3.549999698556466</v>
       </c>
       <c r="C2" t="n">
-        <v>10.389835954044</v>
+        <v>14.0959335375757</v>
       </c>
       <c r="D2" t="n">
-        <v>20.6373184909722</v>
+        <v>10.82475018702533</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.164614819143976</v>
+        <v>11.36863841517807</v>
       </c>
       <c r="C3" t="n">
-        <v>8.62465358180823</v>
+        <v>23.67975462643307</v>
       </c>
       <c r="D3" t="n">
-        <v>88.65181769348698</v>
+        <v>51.1883252994287</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.72888306937441</v>
+        <v>33.56595400819845</v>
       </c>
       <c r="C4" t="n">
-        <v>41.84895938892878</v>
+        <v>74.9299300312293</v>
       </c>
       <c r="D4" t="n">
-        <v>215.1794618168159</v>
+        <v>134.1234261110865</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.38882281527331</v>
+        <v>59.56754195517523</v>
       </c>
       <c r="C5" t="n">
-        <v>145.1023106876786</v>
+        <v>193.9933463591698</v>
       </c>
       <c r="D5" t="n">
-        <v>217.7761844945488</v>
+        <v>147.900291644782</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.57245069369646</v>
+        <v>60.86050368166828</v>
       </c>
       <c r="C6" t="n">
-        <v>285.7867567062465</v>
+        <v>341.3742934684052</v>
       </c>
       <c r="D6" t="n">
-        <v>124.9813914891402</v>
+        <v>95.4366760775367</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.48228446915921</v>
+        <v>31.9794497181356</v>
       </c>
       <c r="C7" t="n">
-        <v>316.1414139738536</v>
+        <v>346.0248323434222</v>
       </c>
       <c r="D7" t="n">
-        <v>57.9103518304066</v>
+        <v>52.28101049425539</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>223.1414356982575</v>
+        <v>246.8408252787755</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>106.1671784849543</v>
+        <v>127.578114166873</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>51.53193699591508</v>
       </c>
       <c r="D10" t="n">
         <v>26.33538216642069</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.083890523217484</v>
+        <v>6.131996160725578</v>
       </c>
       <c r="C2" t="n">
-        <v>4.003567137918493</v>
+        <v>7.723409189309657</v>
       </c>
       <c r="D2" t="n">
-        <v>8.992808970900782</v>
+        <v>13.26341148437441</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.143155238370787</v>
+        <v>2.567270246605409</v>
       </c>
       <c r="C2" t="n">
-        <v>5.983752257384309</v>
+        <v>8.120035261825368</v>
       </c>
       <c r="D2" t="n">
-        <v>15.35453409442012</v>
+        <v>8.054258165640832</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.56637061435917</v>
+        <v>15.28581175512284</v>
       </c>
       <c r="C3" t="n">
-        <v>19.08517537055799</v>
+        <v>36.24612524079224</v>
       </c>
       <c r="D3" t="n">
-        <v>96.44198572668542</v>
+        <v>55.63564239966675</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.77689089589127</v>
+        <v>45.76711447657781</v>
       </c>
       <c r="C4" t="n">
-        <v>66.22575488537709</v>
+        <v>109.797681495259</v>
       </c>
       <c r="D4" t="n">
-        <v>219.289057706793</v>
+        <v>138.194733840598</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.55751918948773</v>
+        <v>35.36746104549135</v>
       </c>
       <c r="C5" t="n">
-        <v>231.643370817035</v>
+        <v>290.0082718345078</v>
       </c>
       <c r="D5" t="n">
-        <v>194.1406085148068</v>
+        <v>134.9903093339364</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.91827826083604</v>
+        <v>19.84406634594078</v>
       </c>
       <c r="C6" t="n">
-        <v>261.4345049024045</v>
+        <v>291.4622401844974</v>
       </c>
       <c r="D6" t="n">
-        <v>94.3901330248096</v>
+        <v>76.71965609607126</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>156.9029180927252</v>
+        <v>173.5513956613426</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>78.1912959047372</v>
+        <v>94.04652132832319</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>39.2718716652809</v>
       </c>
       <c r="D9" t="n">
         <v>20.07968579496001</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
         <v>19.21771131063132</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
         <v>16.34806277111788</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.624833508257476</v>
+        <v>6.849653732529996</v>
       </c>
       <c r="C2" t="n">
-        <v>5.563564239966674</v>
+        <v>6.823146544515332</v>
       </c>
       <c r="D2" t="n">
-        <v>10.98575681052181</v>
+        <v>17.64789673154067</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.92470852640926</v>
+        <v>13.02288329683394</v>
       </c>
       <c r="C3" t="n">
-        <v>10.08745766113598</v>
+        <v>19.45823949817178</v>
       </c>
       <c r="D3" t="n">
-        <v>10.69123249924777</v>
+        <v>14.27952035826986</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39872693348748</v>
+        <v>13.39734692852471</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1462762988462</v>
+        <v>70.13905156698232</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576320815704409</v>
+        <v>1.576158462179378</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.524875168873549</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C2" t="n">
-        <v>5.393721887131976</v>
+        <v>5.269039928692631</v>
       </c>
       <c r="D2" t="n">
-        <v>27.15710499487527</v>
+        <v>15.12284163621787</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.90846078379357</v>
+        <v>19.40915211295944</v>
       </c>
       <c r="C3" t="n">
-        <v>17.47510913559323</v>
+        <v>23.930100291016</v>
       </c>
       <c r="D3" t="n">
-        <v>17.33275571847744</v>
+        <v>25.65306751196916</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.02172162268045</v>
+        <v>15.14934882423253</v>
       </c>
       <c r="C4" t="n">
-        <v>16.15760371649401</v>
+        <v>30.2093586073786</v>
       </c>
       <c r="D4" t="n">
-        <v>20.67560665143782</v>
+        <v>22.55172651425348</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44421849143824</v>
+        <v>15.4386420485654</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16248211012912</v>
+        <v>86.13137142883858</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251414419250156</v>
+        <v>3.250240431276927</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.557272843113694</v>
+        <v>4.771293842639499</v>
       </c>
       <c r="C2" t="n">
-        <v>5.253331965424683</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="D2" t="n">
-        <v>41.15191851891355</v>
+        <v>17.14720540237479</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0824100538945</v>
+        <v>17.35239067256238</v>
       </c>
       <c r="C3" t="n">
-        <v>19.6055016538088</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D3" t="n">
-        <v>35.03366682604743</v>
+        <v>31.79880814055419</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.17183121043897</v>
+        <v>27.89930625928586</v>
       </c>
       <c r="C4" t="n">
-        <v>32.39178375391926</v>
+        <v>47.7070479401695</v>
       </c>
       <c r="D4" t="n">
-        <v>24.72138894063893</v>
+        <v>30.33698580893068</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.32722508515045</v>
+        <v>13.17996292951343</v>
       </c>
       <c r="C5" t="n">
-        <v>19.26679869584366</v>
+        <v>34.09118902997049</v>
       </c>
       <c r="D5" t="n">
-        <v>29.86967390170921</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5263,7 +5263,7 @@
         <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74032089860937</v>
+        <v>16.73083092927667</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1159574815171</v>
+        <v>102.0580686685877</v>
       </c>
       <c r="D21" t="n">
-        <v>5.02209626958281</v>
+        <v>4.182707732319169</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.957245069369645</v>
+        <v>5.169883410563703</v>
       </c>
       <c r="C2" t="n">
-        <v>6.571819132228149</v>
+        <v>4.469897297435728</v>
       </c>
       <c r="D2" t="n">
-        <v>43.01625740927824</v>
+        <v>17.80693985962865</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.27737693641212</v>
+        <v>16.80261195818416</v>
       </c>
       <c r="C3" t="n">
-        <v>20.04728812071987</v>
+        <v>18.47649179392497</v>
       </c>
       <c r="D3" t="n">
-        <v>58.51707191163113</v>
+        <v>37.75801670533232</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.51566389110361</v>
+        <v>31.12827445855362</v>
       </c>
       <c r="C4" t="n">
-        <v>41.69580674706629</v>
+        <v>51.61244030766331</v>
       </c>
       <c r="D4" t="n">
-        <v>36.06744715861932</v>
+        <v>38.95182191369645</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.92443078896878</v>
+        <v>27.36621725587985</v>
       </c>
       <c r="C5" t="n">
-        <v>40.96342295969817</v>
+        <v>62.93002784222056</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71045084717198</v>
+        <v>34.28753857081986</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.03524510636165</v>
+        <v>11.95474179461341</v>
       </c>
       <c r="C6" t="n">
-        <v>21.89690079552086</v>
+        <v>34.29441080474959</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06756046086043</v>
+        <v>18.05592525187138</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8693230065657</v>
+        <v>117.7934171193514</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882880175565878</v>
+        <v>6.018641750623793</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.622469102221483</v>
+        <v>5.849252821902496</v>
       </c>
       <c r="C2" t="n">
-        <v>12.51924672455533</v>
+        <v>7.847109400044756</v>
       </c>
       <c r="D2" t="n">
-        <v>34.85400699617026</v>
+        <v>27.21502810942583</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.56208377064369</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="C3" t="n">
-        <v>21.78498155723672</v>
+        <v>16.75352457297182</v>
       </c>
       <c r="D3" t="n">
-        <v>73.55744674069227</v>
+        <v>40.35473938306514</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.46238747316702</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="C4" t="n">
-        <v>38.86248287260999</v>
+        <v>40.26638208968293</v>
       </c>
       <c r="D4" t="n">
-        <v>49.0471335564664</v>
+        <v>42.34670547498192</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.48202242725196</v>
+        <v>22.89926520155685</v>
       </c>
       <c r="C5" t="n">
-        <v>44.52225838759286</v>
+        <v>59.98478472948013</v>
       </c>
       <c r="D5" t="n">
-        <v>29.91876128692155</v>
+        <v>32.32404316232624</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.16229147083699</v>
+        <v>13.32329809433347</v>
       </c>
       <c r="C6" t="n">
-        <v>30.10823859384119</v>
+        <v>46.49066253460771</v>
       </c>
       <c r="D6" t="n">
-        <v>30.87302005544945</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>17.00779722837174</v>
+        <v>22.69702517448201</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061709585901287</v>
+        <v>7.057417155219355</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20352736782456</v>
+        <v>66.16328583018145</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296282189425965</v>
+        <v>4.410885722012097</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.218389958699297</v>
+        <v>5.165956419746716</v>
       </c>
       <c r="C2" t="n">
-        <v>5.619523859108742</v>
+        <v>6.858489461868218</v>
       </c>
       <c r="D2" t="n">
-        <v>35.41556668299944</v>
+        <v>24.79207477534471</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55012287174348</v>
+        <v>18.56975782582842</v>
       </c>
       <c r="C3" t="n">
-        <v>39.28463438543612</v>
+        <v>25.87396074542469</v>
       </c>
       <c r="D3" t="n">
-        <v>85.05862109594365</v>
+        <v>54.16302084329652</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.81822211046087</v>
+        <v>27.72062817711294</v>
       </c>
       <c r="C4" t="n">
-        <v>48.80464187351743</v>
+        <v>41.44055234396211</v>
       </c>
       <c r="D4" t="n">
-        <v>75.74674412116265</v>
+        <v>54.2670860999467</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.35425635697964</v>
+        <v>29.84513020910304</v>
       </c>
       <c r="C5" t="n">
-        <v>60.84381397069608</v>
+        <v>69.11503837897546</v>
       </c>
       <c r="D5" t="n">
-        <v>41.96971435655115</v>
+        <v>41.23340357836604</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.98369550412208</v>
+        <v>23.74847696573035</v>
       </c>
       <c r="C6" t="n">
-        <v>54.42023874180921</v>
+        <v>75.79386801096652</v>
       </c>
       <c r="D6" t="n">
-        <v>33.89189424600839</v>
+        <v>34.89818564286137</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>11.5581157220977</v>
       </c>
       <c r="C7" t="n">
-        <v>32.75797564760332</v>
+        <v>49.0471335564664</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>21.36283004441059</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
         <v>24.76949457814703</v>
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.284023723618187</v>
+        <v>7.281261830125426</v>
       </c>
       <c r="C21" t="n">
-        <v>75.57174613253869</v>
+        <v>75.54309148755129</v>
       </c>
       <c r="D21" t="n">
-        <v>6.373520758165913</v>
+        <v>5.460946372594069</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.721625620350411</v>
+        <v>4.497386233154638</v>
       </c>
       <c r="C2" t="n">
-        <v>6.46677212787374</v>
+        <v>6.104507225006667</v>
       </c>
       <c r="D2" t="n">
-        <v>41.91473648511332</v>
+        <v>19.1126643062769</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.24363766156923</v>
+        <v>18.24087234490574</v>
       </c>
       <c r="C3" t="n">
-        <v>28.72102908774044</v>
+        <v>26.6397239547372</v>
       </c>
       <c r="D3" t="n">
-        <v>93.65382224662449</v>
+        <v>61.42795385472292</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.14478424307656</v>
+        <v>32.83847895935156</v>
       </c>
       <c r="C4" t="n">
-        <v>77.99298286847934</v>
+        <v>54.80312034646545</v>
       </c>
       <c r="D4" t="n">
-        <v>101.3615234726662</v>
+        <v>68.71448531564275</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.81553890925539</v>
+        <v>36.66827675361837</v>
       </c>
       <c r="C5" t="n">
-        <v>77.63169971331654</v>
+        <v>73.55744674069228</v>
       </c>
       <c r="D5" t="n">
-        <v>59.19938656608268</v>
+        <v>52.0817157102933</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.32207966691774</v>
+        <v>32.8453511932813</v>
       </c>
       <c r="C6" t="n">
-        <v>77.72594749292425</v>
+        <v>95.07441117466963</v>
       </c>
       <c r="D6" t="n">
-        <v>39.7686360036298</v>
+        <v>40.37241084174159</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="C7" t="n">
-        <v>57.43125895073415</v>
+        <v>82.70340835345554</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>33.71321616383547</v>
+        <v>47.14843349645307</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>28.6218725696115</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6490,7 +6490,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
         <v>27.18950266911542</v>
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.493087598475137</v>
+        <v>7.493298985673709</v>
       </c>
       <c r="C21" t="n">
-        <v>85.23387143265468</v>
+        <v>85.23627596203845</v>
       </c>
       <c r="D21" t="n">
-        <v>7.493087598475137</v>
+        <v>6.556636612464496</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_52_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630435789</v>
+        <v>10.84497646421511</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907184484182</v>
+        <v>37.78907240186064</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.931719629059228</v>
+        <v>0.947386534598172</v>
       </c>
       <c r="C2" t="n">
-        <v>14.82635382953533</v>
+        <v>3.179880814055419</v>
       </c>
       <c r="D2" t="n">
-        <v>27.55078582427824</v>
+        <v>18.40187896840222</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.66516727958961</v>
+        <v>7.058765993534568</v>
       </c>
       <c r="C3" t="n">
-        <v>24.93639168786898</v>
+        <v>37.04624961975339</v>
       </c>
       <c r="D3" t="n">
-        <v>62.29189183446012</v>
+        <v>91.49888603580274</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.97436105316512</v>
+        <v>11.2184310164283</v>
       </c>
       <c r="C4" t="n">
-        <v>60.76331065894783</v>
+        <v>99.15357288581511</v>
       </c>
       <c r="D4" t="n">
-        <v>83.21293541195965</v>
+        <v>99.95762425559325</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.51596699073988</v>
+        <v>10.21017612416683</v>
       </c>
       <c r="C5" t="n">
-        <v>88.52909923045614</v>
+        <v>107.4522862298134</v>
       </c>
       <c r="D5" t="n">
-        <v>63.81360077604268</v>
+        <v>56.89227946110267</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.45920555034281</v>
+        <v>8.010079518949729</v>
       </c>
       <c r="C6" t="n">
-        <v>106.7876430340383</v>
+        <v>59.49194738194822</v>
       </c>
       <c r="D6" t="n">
-        <v>47.57745724320893</v>
+        <v>30.51075515258238</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.42239785920016</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>110.6105685943754</v>
+        <v>35.33309987584271</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.02212253330794</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>79.77681844709581</v>
+        <v>28.45595720759379</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>44.26405874137593</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.692431537298059</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.23228633190121</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.692431537298059</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.576147033672636</v>
+        <v>0.6597344572538566</v>
       </c>
       <c r="C2" t="n">
-        <v>17.68127615348505</v>
+        <v>9.836130248848793</v>
       </c>
       <c r="D2" t="n">
-        <v>28.15063367157304</v>
+        <v>23.62281325958675</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.19669369821463</v>
+        <v>5.026548245743669</v>
       </c>
       <c r="C3" t="n">
-        <v>41.97462309507238</v>
+        <v>22.66855449105885</v>
       </c>
       <c r="D3" t="n">
-        <v>68.36400138522664</v>
+        <v>85.13225217376217</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.58322455624739</v>
+        <v>12.63509295365645</v>
       </c>
       <c r="C4" t="n">
-        <v>61.49078570779472</v>
+        <v>96.48616437337652</v>
       </c>
       <c r="D4" t="n">
-        <v>92.73392464774521</v>
+        <v>122.0754182845696</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.92754026299754</v>
+        <v>13.54811831860599</v>
       </c>
       <c r="C5" t="n">
-        <v>99.15651812892787</v>
+        <v>148.3420781116931</v>
       </c>
       <c r="D5" t="n">
-        <v>77.55806863549803</v>
+        <v>78.53981633974485</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.11331156327844</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>123.4115769100496</v>
+        <v>117.6958417759246</v>
       </c>
       <c r="D6" t="n">
-        <v>55.2252718592916</v>
+        <v>40.33215918586747</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.34550274309942</v>
+        <v>7.60559946480004</v>
       </c>
       <c r="C7" t="n">
-        <v>131.2115624202904</v>
+        <v>61.14422876819559</v>
       </c>
       <c r="D7" t="n">
-        <v>44.13643153982385</v>
+        <v>31.68001666834032</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.94973524510094</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>112.4886519525995</v>
+        <v>38.30288668118931</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.87031149204818</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>69.77968157475051</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.876204058266429</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.3751782647469</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.860729565549732</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.659996499161114</v>
+        <v>0.3495021827118645</v>
       </c>
       <c r="C2" t="n">
-        <v>11.96946801017711</v>
+        <v>4.12137686242811</v>
       </c>
       <c r="D2" t="n">
-        <v>25.86021627756523</v>
+        <v>16.07906390015426</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.42664364518664</v>
+        <v>4.363868545377072</v>
       </c>
       <c r="C3" t="n">
-        <v>54.29064804484862</v>
+        <v>31.94116155766998</v>
       </c>
       <c r="D3" t="n">
-        <v>73.14511270490861</v>
+        <v>86.90921551844889</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.80019079888594</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="C4" t="n">
-        <v>80.66039138091794</v>
+        <v>89.31351564614933</v>
       </c>
       <c r="D4" t="n">
-        <v>102.9696262122225</v>
+        <v>134.6977485180709</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.49204519293946</v>
+        <v>13.69538047424301</v>
       </c>
       <c r="C5" t="n">
-        <v>105.3415286656828</v>
+        <v>176.6164119940012</v>
       </c>
       <c r="D5" t="n">
-        <v>88.94634200476104</v>
+        <v>88.82362354173019</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.6680400739069</v>
+        <v>9.539642442166258</v>
       </c>
       <c r="C6" t="n">
-        <v>137.2581465307466</v>
+        <v>151.8694976130519</v>
       </c>
       <c r="D6" t="n">
-        <v>64.84541761320608</v>
+        <v>40.73467574460867</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.08894779712151</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>151.3933499764921</v>
+        <v>60.96456893831842</v>
       </c>
       <c r="D7" t="n">
-        <v>48.44826745687584</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.21114217633784</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>140.6942634956104</v>
+        <v>38.88702656521616</v>
       </c>
       <c r="D8" t="n">
-        <v>40.97324043674063</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.9734360587231</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>99.51092905016091</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>59.36137493728339</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.043598413473706</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6049279869477</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.05449801684213</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.849072895453248</v>
+        <v>0.3544109212330985</v>
       </c>
       <c r="C2" t="n">
-        <v>8.138688468206057</v>
+        <v>4.913647259755286</v>
       </c>
       <c r="D2" t="n">
-        <v>21.24894731071796</v>
+        <v>16.34119053718816</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.43570035870311</v>
+        <v>2.743984833369835</v>
       </c>
       <c r="C3" t="n">
-        <v>71.80502708861171</v>
+        <v>23.16924582022473</v>
       </c>
       <c r="D3" t="n">
-        <v>79.19267856306897</v>
+        <v>80.63093894979055</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.80698091735765</v>
+        <v>11.25671917689393</v>
       </c>
       <c r="C4" t="n">
-        <v>97.494419265638</v>
+        <v>85.06352983446489</v>
       </c>
       <c r="D4" t="n">
-        <v>100.1745904982318</v>
+        <v>146.3628747399315</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.34229545807943</v>
+        <v>17.32784697995621</v>
       </c>
       <c r="C5" t="n">
-        <v>82.00047699721485</v>
+        <v>172.2476347101029</v>
       </c>
       <c r="D5" t="n">
-        <v>62.63550353094652</v>
+        <v>113.88273369263</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.82647700272235</v>
+        <v>13.4038014060817</v>
       </c>
       <c r="C6" t="n">
-        <v>99.70335160019334</v>
+        <v>215.3061072706638</v>
       </c>
       <c r="D6" t="n">
-        <v>31.87931145230244</v>
+        <v>56.67433147075987</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.31963314542373</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>98.93267965235957</v>
+        <v>134.8646456277928</v>
       </c>
       <c r="D7" t="n">
-        <v>28.80545939030566</v>
+        <v>36.89015173477814</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>73.35127972280043</v>
+        <v>58.4974369575462</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>45.26249615659493</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.89551813718911</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.728096943652639</v>
+        <v>0.2709623663721197</v>
       </c>
       <c r="C2" t="n">
-        <v>3.771874679716245</v>
+        <v>2.533890824661018</v>
       </c>
       <c r="D2" t="n">
-        <v>14.42776426161113</v>
+        <v>13.4038014060817</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.29611225825082</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C3" t="n">
-        <v>52.0817157102933</v>
+        <v>21.392282475538</v>
       </c>
       <c r="D3" t="n">
-        <v>78.30910562924683</v>
+        <v>76.9052064121739</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.96610616090365</v>
+        <v>9.125344910974103</v>
       </c>
       <c r="C4" t="n">
-        <v>141.1684476367616</v>
+        <v>74.30455674362409</v>
       </c>
       <c r="D4" t="n">
-        <v>115.2856511619987</v>
+        <v>152.4251668136555</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.23845118560752</v>
+        <v>18.26050729899067</v>
       </c>
       <c r="C5" t="n">
-        <v>127.7744637077224</v>
+        <v>171.683129780161</v>
       </c>
       <c r="D5" t="n">
-        <v>78.14711725804612</v>
+        <v>133.5176877775662</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="C6" t="n">
-        <v>116.810305346694</v>
+        <v>250.1237896017769</v>
       </c>
       <c r="D6" t="n">
-        <v>39.20511282139213</v>
+        <v>69.55486135047803</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>121.1506119471691</v>
+        <v>196.7275137154971</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>41.08221443191203</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>94.29686699290613</v>
+        <v>89.20650514638642</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>51.58593311964863</v>
+        <v>46.03905859065416</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.841979677345269</v>
+        <v>0.9581857593448869</v>
       </c>
       <c r="C2" t="n">
-        <v>5.134540493210818</v>
+        <v>5.285729639664827</v>
       </c>
       <c r="D2" t="n">
-        <v>11.08196808553799</v>
+        <v>26.31869245544849</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.34810382884689</v>
+        <v>1.506982726018854</v>
       </c>
       <c r="C3" t="n">
-        <v>32.34367811641117</v>
+        <v>15.54106615822701</v>
       </c>
       <c r="D3" t="n">
-        <v>72.20754364735291</v>
+        <v>70.3913103944963</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.00661985868502</v>
+        <v>6.662139921018855</v>
       </c>
       <c r="C4" t="n">
-        <v>135.4124608467626</v>
+        <v>63.96675341790518</v>
       </c>
       <c r="D4" t="n">
-        <v>126.1850141745468</v>
+        <v>155.5392705315264</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.30703465618456</v>
+        <v>16.64062358698344</v>
       </c>
       <c r="C5" t="n">
-        <v>192.6925306510427</v>
+        <v>155.1161372709961</v>
       </c>
       <c r="D5" t="n">
-        <v>97.80661503558851</v>
+        <v>153.9625837185061</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.05668899160162</v>
+        <v>20.04532462531138</v>
       </c>
       <c r="C6" t="n">
-        <v>158.6317757999039</v>
+        <v>263.7691009431033</v>
       </c>
       <c r="D6" t="n">
-        <v>51.4818678629985</v>
+        <v>90.12345750215297</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.80545939030566</v>
+        <v>12.15698182168825</v>
       </c>
       <c r="C7" t="n">
-        <v>144.9854827108732</v>
+        <v>268.8309921061999</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>49.1669067763845</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>125.0893837366073</v>
+        <v>162.4743363143259</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>41.97462309507237</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>79.5421807457808</v>
+        <v>72.77499382040753</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>43.37655881673681</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>45.12603322570465</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.869648539513427</v>
+        <v>0.6508987279156352</v>
       </c>
       <c r="C2" t="n">
-        <v>2.393500902953724</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="D2" t="n">
-        <v>7.750898125028567</v>
+        <v>19.15978819608075</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.4364611222291</v>
+        <v>2.596722677732814</v>
       </c>
       <c r="C3" t="n">
-        <v>29.11863690796039</v>
+        <v>19.65458903902115</v>
       </c>
       <c r="D3" t="n">
-        <v>68.84014902178635</v>
+        <v>79.91917186421159</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.05240214788613</v>
+        <v>11.25671917689393</v>
       </c>
       <c r="C4" t="n">
-        <v>128.8396599668302</v>
+        <v>88.90510860118265</v>
       </c>
       <c r="D4" t="n">
-        <v>134.2000024320178</v>
+        <v>159.5212392199515</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.46687960552754</v>
+        <v>12.19821522526662</v>
       </c>
       <c r="C5" t="n">
-        <v>236.404847182632</v>
+        <v>227.0046129144688</v>
       </c>
       <c r="D5" t="n">
-        <v>103.3044021793706</v>
+        <v>140.1935721664445</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.57617239586842</v>
+        <v>7.527059648460297</v>
       </c>
       <c r="C6" t="n">
-        <v>192.8054316370311</v>
+        <v>239.0948358922683</v>
       </c>
       <c r="D6" t="n">
-        <v>50.59633143376788</v>
+        <v>72.8554971321558</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>3.772856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>155.8848457234213</v>
+        <v>114.2636518018778</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>96.63342652901355</v>
+        <v>53.57397222074844</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>34.40043955680824</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.463605900582747</v>
+        <v>0.3406664533736432</v>
       </c>
       <c r="C2" t="n">
-        <v>9.512153506447346</v>
+        <v>1.81917849596934</v>
       </c>
       <c r="D2" t="n">
-        <v>9.852819959820989</v>
+        <v>13.75624883190631</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.84540794654352</v>
+        <v>2.400373136883451</v>
       </c>
       <c r="C3" t="n">
-        <v>19.04099672386689</v>
+        <v>15.19254572321939</v>
       </c>
       <c r="D3" t="n">
-        <v>60.78000036992003</v>
+        <v>77.22918315457534</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.45706212848506</v>
+        <v>7.67039481328033</v>
       </c>
       <c r="C4" t="n">
-        <v>102.3953038052381</v>
+        <v>65.8045851202552</v>
       </c>
       <c r="D4" t="n">
-        <v>136.9950381460084</v>
+        <v>155.7051858935441</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.52979357405735</v>
+        <v>11.46190444708151</v>
       </c>
       <c r="C5" t="n">
-        <v>236.5030219530567</v>
+        <v>178.3835578616455</v>
       </c>
       <c r="D5" t="n">
-        <v>122.4484824121835</v>
+        <v>145.1513980728909</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.71329827929349</v>
+        <v>7.205046401467343</v>
       </c>
       <c r="C6" t="n">
-        <v>277.1326506933109</v>
+        <v>241.1476703418483</v>
       </c>
       <c r="D6" t="n">
-        <v>65.89196066593318</v>
+        <v>79.49702035138549</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>2.994330497952772</v>
       </c>
       <c r="C7" t="n">
-        <v>208.6449490973491</v>
+        <v>154.6871135242402</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>142.196337483108</v>
+        <v>59.83261383532185</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>65.78593191387449</v>
+        <v>28.84374755077128</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>17.93653055658923</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.398409641474958</v>
+        <v>0.1767145867644259</v>
       </c>
       <c r="C2" t="n">
-        <v>4.953898915629405</v>
+        <v>4.897939296487337</v>
       </c>
       <c r="D2" t="n">
-        <v>8.244717220264713</v>
+        <v>22.2081148177671</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.29915531235479</v>
+        <v>1.742602175038088</v>
       </c>
       <c r="C3" t="n">
-        <v>27.34167356327367</v>
+        <v>10.41634314205866</v>
       </c>
       <c r="D3" t="n">
-        <v>56.67138622764713</v>
+        <v>70.50421138048469</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.39851711912875</v>
+        <v>6.100580234189679</v>
       </c>
       <c r="C4" t="n">
-        <v>81.88561251581795</v>
+        <v>50.66799901617789</v>
       </c>
       <c r="D4" t="n">
-        <v>136.7653091832146</v>
+        <v>159.189408495916</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.17484287347651</v>
+        <v>11.75642875835556</v>
       </c>
       <c r="C5" t="n">
-        <v>226.5873701401639</v>
+        <v>147.7775731817512</v>
       </c>
       <c r="D5" t="n">
-        <v>134.7694161004809</v>
+        <v>167.3879835740812</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.07935130425731</v>
+        <v>11.23021198887927</v>
       </c>
       <c r="C6" t="n">
-        <v>321.8119887135833</v>
+        <v>266.5464651984176</v>
       </c>
       <c r="D6" t="n">
-        <v>78.69198723390311</v>
+        <v>104.2517887139688</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.78632315783946</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>270.7473636248896</v>
+        <v>252.6017208072958</v>
       </c>
       <c r="D7" t="n">
-        <v>44.19631814978291</v>
+        <v>48.44826745687584</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>178.9137016219387</v>
+        <v>132.0990623449296</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>73.99530621678632</v>
+        <v>50.9203081761693</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>22.63124807829746</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.549999698556466</v>
+        <v>0.150207398749762</v>
       </c>
       <c r="C2" t="n">
-        <v>14.0959335375757</v>
+        <v>8.844565067559515</v>
       </c>
       <c r="D2" t="n">
-        <v>10.82475018702533</v>
+        <v>23.74651347032185</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.36863841517807</v>
+        <v>1.148644813968768</v>
       </c>
       <c r="C3" t="n">
-        <v>23.67975462643307</v>
+        <v>14.98637870532756</v>
       </c>
       <c r="D3" t="n">
-        <v>51.1883252994287</v>
+        <v>71.4859590847315</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.56595400819845</v>
+        <v>4.722206457427157</v>
       </c>
       <c r="C4" t="n">
-        <v>74.9299300312293</v>
+        <v>37.8287025400381</v>
       </c>
       <c r="D4" t="n">
-        <v>134.1234261110865</v>
+        <v>158.51298432769</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.56754195517523</v>
+        <v>10.60287520586555</v>
       </c>
       <c r="C5" t="n">
-        <v>193.9933463591698</v>
+        <v>120.5340743889022</v>
       </c>
       <c r="D5" t="n">
-        <v>147.900291644782</v>
+        <v>184.9367237874929</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.86050368166828</v>
+        <v>13.52455637370406</v>
       </c>
       <c r="C6" t="n">
-        <v>341.3742934684052</v>
+        <v>252.6998955777206</v>
       </c>
       <c r="D6" t="n">
-        <v>95.4366760775367</v>
+        <v>127.9600140238251</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.9794497181356</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>346.0248323434222</v>
+        <v>314.8837951647134</v>
       </c>
       <c r="D7" t="n">
-        <v>52.28101049425539</v>
+        <v>64.67753875577986</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>246.8408252787755</v>
+        <v>228.982834538526</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>127.578114166873</v>
+        <v>103.393741220457</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>24.62812290873548</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>51.53193699591508</v>
+        <v>41.70955121492574</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.131996160725578</v>
+        <v>2.731222113214627</v>
       </c>
       <c r="C2" t="n">
-        <v>7.723409189309657</v>
+        <v>7.042076282562371</v>
       </c>
       <c r="D2" t="n">
-        <v>13.26341148437441</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.567270246605409</v>
+        <v>0.2356194490192345</v>
       </c>
       <c r="C2" t="n">
-        <v>8.120035261825368</v>
+        <v>11.40496308023519</v>
       </c>
       <c r="D2" t="n">
-        <v>8.054258165640832</v>
+        <v>23.46573362690726</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.28581175512284</v>
+        <v>0.8295768100885548</v>
       </c>
       <c r="C3" t="n">
-        <v>36.24612524079224</v>
+        <v>24.24916829489622</v>
       </c>
       <c r="D3" t="n">
-        <v>55.63564239966675</v>
+        <v>72.84077091659209</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.76711447657781</v>
+        <v>3.48422260237193</v>
       </c>
       <c r="C4" t="n">
-        <v>109.797681495259</v>
+        <v>37.54792269662352</v>
       </c>
       <c r="D4" t="n">
-        <v>138.194733840598</v>
+        <v>157.8876110400848</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.36746104549135</v>
+        <v>9.203884727313849</v>
       </c>
       <c r="C5" t="n">
-        <v>290.0082718345078</v>
+        <v>96.21127501618744</v>
       </c>
       <c r="D5" t="n">
-        <v>134.9903093339364</v>
+        <v>194.8032882151734</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.84406634594078</v>
+        <v>13.88682127657114</v>
       </c>
       <c r="C6" t="n">
-        <v>291.4622401844974</v>
+        <v>227.0998424417807</v>
       </c>
       <c r="D6" t="n">
-        <v>76.71965609607126</v>
+        <v>151.5072327101848</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>173.5513956613426</v>
+        <v>336.8022944097277</v>
       </c>
       <c r="D7" t="n">
-        <v>32.5184292077671</v>
+        <v>80.6073770048886</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>313.1824263932537</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>42.80910864368217</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>39.2718716652809</v>
+        <v>180.1624847017406</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>74.1661303173253</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.849653732529996</v>
+        <v>2.412154109334413</v>
       </c>
       <c r="C2" t="n">
-        <v>6.823146544515332</v>
+        <v>5.575345212417637</v>
       </c>
       <c r="D2" t="n">
-        <v>17.64789673154067</v>
+        <v>30.15438073594078</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.02288329683394</v>
+        <v>4.520948178056562</v>
       </c>
       <c r="C3" t="n">
-        <v>19.45823949817178</v>
+        <v>13.90154749213484</v>
       </c>
       <c r="D3" t="n">
-        <v>14.27952035826986</v>
+        <v>12.13440162449058</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39734692852471</v>
+        <v>11.67806842227236</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13905156698232</v>
+        <v>59.9474179009981</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576158462179378</v>
+        <v>0.7785378948181571</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.551382356888213</v>
+        <v>1.758310138306037</v>
       </c>
       <c r="C2" t="n">
-        <v>5.269039928692631</v>
+        <v>7.533931882390022</v>
       </c>
       <c r="D2" t="n">
-        <v>15.12284163621787</v>
+        <v>23.13586639828033</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.40915211295944</v>
+        <v>6.980226177194822</v>
       </c>
       <c r="C3" t="n">
-        <v>23.930100291016</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="D3" t="n">
-        <v>25.65306751196916</v>
+        <v>35.61780671007428</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.14934882423253</v>
+        <v>5.781512230309467</v>
       </c>
       <c r="C4" t="n">
-        <v>30.2093586073786</v>
+        <v>23.15157436154828</v>
       </c>
       <c r="D4" t="n">
-        <v>22.55172651425348</v>
+        <v>20.65008121112741</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4386420485654</v>
+        <v>13.62857172237744</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13137142883858</v>
+        <v>73.75462343874847</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250240431276927</v>
+        <v>1.603361379103228</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.771293842639499</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C2" t="n">
-        <v>4.128249096357838</v>
+        <v>8.019896995992195</v>
       </c>
       <c r="D2" t="n">
-        <v>17.14720540237479</v>
+        <v>26.58572783100362</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.35239067256238</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C3" t="n">
-        <v>21.853703896534</v>
+        <v>25.97213551584937</v>
       </c>
       <c r="D3" t="n">
-        <v>31.79880814055419</v>
+        <v>46.4464838879166</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.89930625928586</v>
+        <v>10.49095596758142</v>
       </c>
       <c r="C4" t="n">
-        <v>47.7070479401695</v>
+        <v>38.54341486872977</v>
       </c>
       <c r="D4" t="n">
-        <v>30.33698580893068</v>
+        <v>34.52315801983909</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.17996292951343</v>
+        <v>5.890486225480863</v>
       </c>
       <c r="C5" t="n">
-        <v>34.09118902997049</v>
+        <v>27.66074156715389</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>27.36621725587985</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73083092927667</v>
+        <v>14.84010123069133</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0580686685877</v>
+        <v>87.39170724740453</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182707732319169</v>
+        <v>2.473350205115222</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.169883410563703</v>
+        <v>1.79758004647591</v>
       </c>
       <c r="C2" t="n">
-        <v>4.469897297435728</v>
+        <v>4.855724145204724</v>
       </c>
       <c r="D2" t="n">
-        <v>17.80693985962865</v>
+        <v>33.18209065583794</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.80261195818416</v>
+        <v>6.273367830137119</v>
       </c>
       <c r="C3" t="n">
-        <v>18.47649179392497</v>
+        <v>29.21681167838507</v>
       </c>
       <c r="D3" t="n">
-        <v>37.75801670533232</v>
+        <v>56.93645810779378</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.12827445855362</v>
+        <v>11.85656702418873</v>
       </c>
       <c r="C4" t="n">
-        <v>51.61244030766331</v>
+        <v>54.4330014619644</v>
       </c>
       <c r="D4" t="n">
-        <v>38.95182191369645</v>
+        <v>49.69803228438204</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.36621725587985</v>
+        <v>11.16738013580747</v>
       </c>
       <c r="C5" t="n">
-        <v>62.93002784222056</v>
+        <v>52.94074495150926</v>
       </c>
       <c r="D5" t="n">
-        <v>34.28753857081986</v>
+        <v>34.01755795215198</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.95474179461341</v>
+        <v>6.359761628110839</v>
       </c>
       <c r="C6" t="n">
-        <v>34.29441080474959</v>
+        <v>29.10194719698821</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05592525187138</v>
+        <v>16.08458091427317</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7934171193514</v>
+        <v>101.5868268269885</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018641750623793</v>
+        <v>3.386227560899616</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.849252821902496</v>
+        <v>1.411753198706913</v>
       </c>
       <c r="C2" t="n">
-        <v>7.847109400044756</v>
+        <v>5.413356841216912</v>
       </c>
       <c r="D2" t="n">
-        <v>27.21502810942583</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.40853021815369</v>
+        <v>6.209554229361076</v>
       </c>
       <c r="C3" t="n">
-        <v>16.75352457297182</v>
+        <v>23.40977400776519</v>
       </c>
       <c r="D3" t="n">
-        <v>40.35473938306514</v>
+        <v>69.48810250658924</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.07499804061703</v>
+        <v>12.08629598698248</v>
       </c>
       <c r="C4" t="n">
-        <v>40.26638208968293</v>
+        <v>64.34963502256143</v>
       </c>
       <c r="D4" t="n">
-        <v>42.34670547498192</v>
+        <v>65.6386697582375</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.89926520155685</v>
+        <v>14.50532233024663</v>
       </c>
       <c r="C5" t="n">
-        <v>59.98478472948013</v>
+        <v>79.1534086548991</v>
       </c>
       <c r="D5" t="n">
-        <v>32.32404316232624</v>
+        <v>44.20319038371264</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.32329809433347</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="C6" t="n">
-        <v>46.49066253460771</v>
+        <v>58.12339108222817</v>
       </c>
       <c r="D6" t="n">
-        <v>31.55729820530948</v>
+        <v>37.15227837181205</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>22.69702517448201</v>
+        <v>30.42239785920016</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057417155219355</v>
+        <v>17.35494139146939</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16328583018145</v>
+        <v>115.4103602532714</v>
       </c>
       <c r="D21" t="n">
-        <v>4.410885722012097</v>
+        <v>4.338735347867348</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.165956419746716</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C2" t="n">
-        <v>6.858489461868218</v>
+        <v>13.33606081448867</v>
       </c>
       <c r="D2" t="n">
-        <v>24.79207477534471</v>
+        <v>34.28753857081986</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.56975782582842</v>
+        <v>5.443791020048564</v>
       </c>
       <c r="C3" t="n">
-        <v>25.87396074542469</v>
+        <v>22.03532722181966</v>
       </c>
       <c r="D3" t="n">
-        <v>54.16302084329652</v>
+        <v>80.89601082993718</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.72062817711294</v>
+        <v>11.92038062496477</v>
       </c>
       <c r="C4" t="n">
-        <v>41.44055234396211</v>
+        <v>61.23553130469055</v>
       </c>
       <c r="D4" t="n">
-        <v>54.2670860999467</v>
+        <v>83.51924069568466</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.84513020910304</v>
+        <v>16.41973035352791</v>
       </c>
       <c r="C5" t="n">
-        <v>69.11503837897546</v>
+        <v>98.56746950637979</v>
       </c>
       <c r="D5" t="n">
-        <v>41.23340357836604</v>
+        <v>55.81235698643118</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.74847696573035</v>
+        <v>15.01386764104647</v>
       </c>
       <c r="C6" t="n">
-        <v>75.79386801096652</v>
+        <v>91.89453036061421</v>
       </c>
       <c r="D6" t="n">
-        <v>34.89818564286137</v>
+        <v>42.38499363544755</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.5581157220977</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>49.0471335564664</v>
+        <v>56.77250624118454</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>25.70215489718149</v>
+        <v>32.87873061522568</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.281261830125426</v>
+        <v>18.64494988910397</v>
       </c>
       <c r="C21" t="n">
-        <v>75.54309148755129</v>
+        <v>128.7389397104798</v>
       </c>
       <c r="D21" t="n">
-        <v>5.460946372594069</v>
+        <v>5.327128539743991</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.497386233154638</v>
+        <v>1.71118624850219</v>
       </c>
       <c r="C2" t="n">
-        <v>6.104507225006667</v>
+        <v>8.214283041433063</v>
       </c>
       <c r="D2" t="n">
-        <v>19.1126643062769</v>
+        <v>26.91755855503905</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.24087234490574</v>
+        <v>7.662540831646355</v>
       </c>
       <c r="C3" t="n">
-        <v>26.6397239547372</v>
+        <v>41.33648708731195</v>
       </c>
       <c r="D3" t="n">
-        <v>61.42795385472292</v>
+        <v>89.16232649969533</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.83847895935156</v>
+        <v>7.887361055918874</v>
       </c>
       <c r="C4" t="n">
-        <v>54.80312034646545</v>
+        <v>87.41187034302325</v>
       </c>
       <c r="D4" t="n">
-        <v>68.71448531564275</v>
+        <v>76.14238844597412</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.66827675361837</v>
+        <v>8.443030256522571</v>
       </c>
       <c r="C5" t="n">
-        <v>73.55744674069228</v>
+        <v>54.90424036000288</v>
       </c>
       <c r="D5" t="n">
-        <v>52.0817157102933</v>
+        <v>41.92062697133881</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.8453511932813</v>
+        <v>6.198755004614362</v>
       </c>
       <c r="C6" t="n">
-        <v>95.07441117466963</v>
+        <v>37.39378830705677</v>
       </c>
       <c r="D6" t="n">
-        <v>40.37241084174159</v>
+        <v>25.51954982419159</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.72076704583318</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>82.70340835345554</v>
+        <v>23.1162314441954</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>47.14843349645307</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.493298985673709</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.23627596203845</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.556636612464496</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
